--- a/03_Outputs/Turistica_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
@@ -148,7 +148,7 @@
     <numFmt numFmtId="272" formatCode="#,##0.0"/>
     <numFmt numFmtId="273" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,23 +158,335 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -194,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -203,111 +515,167 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="240" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="246" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="252" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="253" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="254" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="254" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="255" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="256" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="256" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="257" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="258" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="258" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="259" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="260" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="260" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="261" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="263" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="16" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="265" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="266" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="266" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="267" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="268" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="268" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="269" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="270" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="270" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="271" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="19" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="273" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="25" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="34" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="26" fontId="34" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,15 +1001,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="90.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="91.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,31 +1227,29 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURÍSTICA Y AGROECOLÓGICA (tasa agregada: Σ viviendas con déficit / Σ viviendas)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="5">
-        <v>0.0705981382863248</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0.233398448747465</v>
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
+        <v>0.154393190208715</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.269225033859051</v>
       </c>
     </row>
     <row r="10">
@@ -894,7 +1260,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>SUBREGIÓN OCCIDENTE (tasa agregada)</t>
+          <t>PROVINCIA TURÍSTICA Y AGROECOLÓGICA (tasa agregada: Σ viviendas con déficit / Σ viviendas)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -908,10 +1274,10 @@
         </is>
       </c>
       <c r="E10" s="5">
-        <v>0.109308727022505</v>
+        <v>0.0966591536793209</v>
       </c>
       <c r="F10" s="7">
-        <v>0.263967245820988</v>
+        <v>0.24382871023511</v>
       </c>
     </row>
     <row r="11">
@@ -922,23 +1288,51 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>SUBREGIÓN OCCIDENTE (tasa agregada)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" s="5">
+        <v>0.109308727022505</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.263967245820988</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>DEPARTAMENTO (ANTIOQUIA) (tasa agregada)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" s="5">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="5">
         <v>0.0575130095088992</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F12" s="7">
         <v>0.177116307342749</v>
       </c>
     </row>
@@ -951,38 +1345,38 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="137" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="137" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="137" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="137" t="inlineStr">
         <is>
           <t>Predios con uso adecuado del suelo rural</t>
         </is>
@@ -1007,7 +1401,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="112" t="inlineStr">
+      <c r="E2" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1032,7 +1426,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="112">
+      <c r="E3" s="138">
         <v>0.259279457639503</v>
       </c>
     </row>
@@ -1055,7 +1449,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="112">
+      <c r="E4" s="138">
         <v>0.288109614573427</v>
       </c>
     </row>
@@ -1078,7 +1472,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="138">
         <v>0.302273809058651</v>
       </c>
     </row>
@@ -1101,7 +1495,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="138">
         <v>0.310356875673876</v>
       </c>
     </row>
@@ -1124,7 +1518,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="138">
         <v>0.356215421137737</v>
       </c>
     </row>
@@ -1147,10 +1541,33 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="E8" s="138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="138">
+        <v>0.321387787068092</v>
       </c>
     </row>
   </sheetData>
@@ -1162,20 +1579,20 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="140" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="140" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1229,6 +1646,16 @@
       </c>
       <c r="B6">
         <v>0.356215421137737</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.321387787068092</v>
       </c>
     </row>
   </sheetData>
@@ -1240,20 +1667,20 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="142" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1327,6 +1754,16 @@
       </c>
       <c r="B8">
         <v>0.417957821710222</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.533370285052284</v>
       </c>
     </row>
   </sheetData>
@@ -1338,26 +1775,26 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="144" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="144" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1676,6 +2113,51 @@
       </c>
       <c r="C22">
         <v>0.300497069185951</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>0.197305225545038</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>0.0582634956810358</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0.217249847422121</v>
       </c>
     </row>
   </sheetData>
@@ -1687,26 +2169,25 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="146" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="146" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2025,6 +2506,51 @@
       </c>
       <c r="C22">
         <v>2.96064737483386</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>3.72607120920584</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>1.10029490199813</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>4.10272155462578</v>
       </c>
     </row>
   </sheetData>
@@ -2036,20 +2562,20 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="148" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2123,6 +2649,16 @@
       </c>
       <c r="B8">
         <v>0.126002389621432</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.154393190208715</v>
       </c>
     </row>
   </sheetData>
@@ -2134,20 +2670,20 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="150" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2221,6 +2757,16 @@
       </c>
       <c r="B8">
         <v>0.218322123375406</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.269225033859051</v>
       </c>
     </row>
   </sheetData>
@@ -2235,23 +2781,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="152" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="152" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="152" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2269,7 +2815,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.99060169702071</v>
+        <v>0.985433970340966</v>
       </c>
     </row>
     <row r="3">
@@ -2284,7 +2830,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.820998101514742</v>
+        <v>0.862139245940442</v>
       </c>
     </row>
     <row r="4">
@@ -2299,7 +2845,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.70591734360676</v>
+        <v>0.729454750846712</v>
       </c>
     </row>
     <row r="5">
@@ -2314,7 +2860,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.834461940560549</v>
+        <v>0.855856736815265</v>
       </c>
     </row>
     <row r="6">
@@ -2329,7 +2875,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.331808843715237</v>
+        <v>0.34649780959583</v>
       </c>
     </row>
     <row r="7">
@@ -2344,7 +2890,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.294102998152793</v>
+        <v>0.32524470651616</v>
       </c>
     </row>
     <row r="8">
@@ -2449,23 +2995,23 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="154" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="154" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2483,7 +3029,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>13.0181560399089</v>
+        <v>21.6898076584845</v>
       </c>
     </row>
     <row r="3">
@@ -2498,7 +3044,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>38.6540601918846</v>
+        <v>40.9633708857797</v>
       </c>
     </row>
     <row r="4">
@@ -2513,7 +3059,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>62.9410120509248</v>
+        <v>63.7331455205107</v>
       </c>
     </row>
     <row r="5">
@@ -2528,7 +3074,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>46.5824308656337</v>
+        <v>49.6444271317019</v>
       </c>
     </row>
     <row r="6">
@@ -2558,7 +3104,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>53.5783768403641</v>
+        <v>54.9488545470332</v>
       </c>
     </row>
     <row r="8">
@@ -2573,7 +3119,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>8.32937307029902</v>
+        <v>12.5008285389787</v>
       </c>
     </row>
     <row r="9">
@@ -2588,7 +3134,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>39.3454022202241</v>
+        <v>41.8397110085717</v>
       </c>
     </row>
     <row r="10">
@@ -2603,7 +3149,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>41.6677968270623</v>
+        <v>42.9987021559284</v>
       </c>
     </row>
     <row r="11">
@@ -2618,7 +3164,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>16.8296118866458</v>
+        <v>28.4275880622052</v>
       </c>
     </row>
     <row r="12">
@@ -2633,7 +3179,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>20.806054873451</v>
+        <v>20.4646558022147</v>
       </c>
     </row>
     <row r="13">
@@ -2810,20 +3356,20 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="156" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="156" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2897,6 +3443,16 @@
       </c>
       <c r="B8">
         <v>25.9343611549181</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>41.4637249436746</v>
       </c>
     </row>
   </sheetData>
@@ -2908,104 +3464,104 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="74.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (municipal)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (agregado)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (municipal)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (agregado)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (municipal)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (agregado)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (municipal)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (agregado)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (municipal)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (agregado)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (municipal)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (agregado)</t>
         </is>
@@ -3030,50 +3586,50 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>0.988669884909543</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="15">
         <v>0.492105834221465</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" s="16">
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="19">
         <v>0.420180844823367</v>
       </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" s="20">
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="23">
         <v>0.377318611161357</v>
       </c>
-      <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" s="24">
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" s="27">
         <v>0.317237654464973</v>
       </c>
-      <c r="N2" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" s="28">
+      <c r="N2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" s="31">
         <v>0</v>
       </c>
-      <c r="P2" s="30" t="inlineStr">
+      <c r="P2" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3098,50 +3654,50 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>0.997299471146433</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="15">
         <v>0.937149866327989</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" s="16">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="19">
         <v>0.843218515709326</v>
       </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" s="20">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="23">
         <v>0.888490076702521</v>
       </c>
-      <c r="L3" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" s="24">
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" s="27">
         <v>0.328977901401525</v>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" s="28">
+      <c r="N3" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" s="31">
         <v>0.199889405425229</v>
       </c>
-      <c r="P3" s="30" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3166,50 +3722,50 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>0.987557893721163</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="15">
         <v>0.937828722303118</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" s="16">
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="19">
         <v>0.875578937211628</v>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" s="20">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="23">
         <v>0.817764381326644</v>
       </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" s="24">
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" s="27">
         <v>0.398304415712005</v>
       </c>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" s="28">
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" s="31">
         <v>0</v>
       </c>
-      <c r="P4" s="30" t="inlineStr">
+      <c r="P4" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3234,50 +3790,50 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>0.981443854899233</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="15">
         <v>0.959189780471245</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="19">
         <v>0.8988573719695</v>
       </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" s="20">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="23">
         <v>0.993503686753115</v>
       </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" s="24">
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" s="27">
         <v>0.366425679583574</v>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" s="28">
+      <c r="N5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" s="31">
         <v>0.20864857237855</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3302,50 +3858,50 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>0.972532601623716</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" s="12">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="15">
         <v>0.917003762269808</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" s="16">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="19">
         <v>0.658906395858674</v>
       </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" s="20">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="23">
         <v>0.950439874402421</v>
       </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" s="24">
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" s="27">
         <v>0.314078809651778</v>
       </c>
-      <c r="N6" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" s="28">
+      <c r="N6" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" s="31">
         <v>0.515600690220927</v>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3370,50 +3926,50 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>0.98118657827087</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" s="12">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" s="15">
         <v>0.883989641707545</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I7" s="16">
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" s="19">
         <v>0.576711409959106</v>
       </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" s="20">
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="23">
         <v>0.927887625742182</v>
       </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" s="24">
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" s="27">
         <v>0.228821980221073</v>
       </c>
-      <c r="N7" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" s="28">
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" s="31">
         <v>0.60810156706407</v>
       </c>
-      <c r="P7" s="30" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3438,262 +3994,330 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>1</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" s="12">
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" s="15">
         <v>0.784520658625836</v>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" s="19">
         <v>0.730177627383622</v>
       </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K8" s="20">
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" s="23">
         <v>0.943374057465196</v>
       </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M8" s="24">
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" s="27">
         <v>0.370823876557939</v>
       </c>
-      <c r="N8" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O8" s="28">
+      <c r="N8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" s="31">
         <v>0.45328424381224</v>
       </c>
-      <c r="P8" s="30" t="inlineStr">
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="11">
+        <v>0.973642383842483</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" s="15">
+        <v>0.956014056511171</v>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" s="19">
+        <v>0.783161804377199</v>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" s="23">
+        <v>0.904674835427907</v>
+      </c>
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" s="27">
+        <v>0.380014716059403</v>
+      </c>
+      <c r="N9" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" s="31">
+        <v>0.396303059760065</v>
+      </c>
+      <c r="P9" s="33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>PROVINCIA TURÍSTICA Y AGROECOLÓGICA (promedio ponderado; sin ECV oficial)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F9" s="11">
-        <v>0.99060169702071</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" s="15">
-        <v>0.820998101514742</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" s="19">
-        <v>0.70591734360676</v>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L9" s="23">
-        <v>0.834461940560549</v>
-      </c>
-      <c r="M9" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N9" s="27">
-        <v>0.331808843715237</v>
-      </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" s="31">
-        <v>0.294102998152793</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" s="14">
+        <v>0.985433970340966</v>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H10" s="18">
+        <v>0.862139245940442</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" s="22">
+        <v>0.729454750846712</v>
+      </c>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" s="26">
+        <v>0.855856736815265</v>
+      </c>
+      <c r="M10" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" s="30">
+        <v>0.34649780959583</v>
+      </c>
+      <c r="O10" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" s="34">
+        <v>0.32524470651616</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>SUBREGIÓN OCCIDENTE (ECV oficial)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F10" s="11">
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" s="14">
         <v>0.975014049622315</v>
       </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" s="15">
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H11" s="18">
         <v>0.820279523369767</v>
       </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J10" s="19">
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" s="22">
         <v>0.650641830743369</v>
       </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L10" s="23">
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" s="26">
         <v>0.801509906445029</v>
       </c>
-      <c r="M10" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N10" s="27">
+      <c r="M11" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" s="30">
         <v>0.320985901103542</v>
       </c>
-      <c r="O10" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P10" s="31">
+      <c r="O11" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" s="34">
         <v>0.309591764699951</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>DEPARTAMENTO (ANTIOQUIA) (ECV oficial)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F11" s="11">
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" s="14">
         <v>0.992586544500931</v>
       </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H11" s="15">
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H12" s="18">
         <v>0.93579635079431</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J11" s="19">
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" s="22">
         <v>0.866893560801633</v>
       </c>
-      <c r="K11" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L11" s="23">
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" s="26">
         <v>0.944698426552535</v>
       </c>
-      <c r="M11" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N11" s="27">
+      <c r="M12" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" s="30">
         <v>0.601239746666835</v>
       </c>
-      <c r="O11" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P11" s="31">
+      <c r="O12" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" s="34">
         <v>0.66955125810138</v>
       </c>
     </row>
@@ -3706,20 +4330,20 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="158" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="158" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3793,6 +4417,16 @@
       </c>
       <c r="B8">
         <v>77.79</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>87.64</v>
       </c>
     </row>
   </sheetData>
@@ -3807,17 +4441,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="160" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3830,7 +4464,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>71.9623830651461</v>
+        <v>80.5050254727946</v>
       </c>
     </row>
     <row r="3">
@@ -3840,7 +4474,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>20.0833658803312</v>
+        <v>42.7570009450461</v>
       </c>
     </row>
     <row r="4">
@@ -3850,7 +4484,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>21.389136697391</v>
+        <v>37.7235646704831</v>
       </c>
     </row>
     <row r="5">
@@ -3860,7 +4494,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>47.0526038119044</v>
+        <v>54.3063612465919</v>
       </c>
     </row>
     <row r="6">
@@ -3870,7 +4504,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>40.0164197781597</v>
+        <v>56.2815979969367</v>
       </c>
     </row>
     <row r="7">
@@ -3880,7 +4514,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>49.9566942665209</v>
+        <v>65.2041408227333</v>
       </c>
     </row>
     <row r="8">
@@ -3890,7 +4524,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>13.5224633650992</v>
+        <v>19.5575234360573</v>
       </c>
     </row>
     <row r="9">
@@ -3900,7 +4534,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>62.3036156850492</v>
+        <v>71.9305612704896</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +4544,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>41.5432229339166</v>
+        <v>58.3029649463931</v>
       </c>
     </row>
     <row r="11">
@@ -3920,7 +4554,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>66.67</v>
+        <v>94.1565685640362</v>
       </c>
     </row>
     <row r="12">
@@ -3930,7 +4564,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>66.4046816272386</v>
+        <v>81.0749459000825</v>
       </c>
     </row>
   </sheetData>
@@ -3942,20 +4576,20 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="162" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="162" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -4029,6 +4663,16 @@
       </c>
       <c r="B8">
         <v>0.299270072992701</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.380782918149466</v>
       </c>
     </row>
   </sheetData>
@@ -4040,20 +4684,20 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="164" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="164" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -4066,7 +4710,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>363.231956423059</v>
+        <v>105.946436677258</v>
       </c>
     </row>
     <row r="3">
@@ -4076,7 +4720,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>589.042182048842</v>
+        <v>200.364732001269</v>
       </c>
     </row>
     <row r="4">
@@ -4086,7 +4730,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>230.324797001874</v>
+        <v>62.4609618988132</v>
       </c>
     </row>
     <row r="5">
@@ -4096,7 +4740,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>604.803493449782</v>
+        <v>195.712584358873</v>
       </c>
     </row>
     <row r="6">
@@ -4106,7 +4750,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>134.909195733641</v>
+        <v>50.4468146439896</v>
       </c>
     </row>
     <row r="7">
@@ -4116,7 +4760,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>174.588757695025</v>
+        <v>52.1747905944091</v>
       </c>
     </row>
     <row r="8">
@@ -4126,7 +4770,17 @@
         </is>
       </c>
       <c r="B8">
-        <v>401.853366039793</v>
+        <v>117.470700463342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>149.115090953872</v>
       </c>
     </row>
   </sheetData>
@@ -4138,20 +4792,20 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="166" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="166" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -4164,7 +4818,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.21469632591852</v>
+        <v>0.388174807197943</v>
       </c>
     </row>
     <row r="3">
@@ -4174,7 +4828,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.0158836990173644</v>
+        <v>0.00158290462999604</v>
       </c>
     </row>
     <row r="4">
@@ -4184,7 +4838,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0928813559322034</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="5">
@@ -4194,7 +4848,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.0127994748933377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4204,7 +4858,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.0384615384615385</v>
+        <v>0.0114285714285714</v>
       </c>
     </row>
     <row r="7">
@@ -4214,7 +4868,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.459537572254335</v>
+        <v>0.733075435203095</v>
       </c>
     </row>
     <row r="8">
@@ -4224,7 +4878,17 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.209983722192078</v>
+        <v>0.0983758700696056</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.852996696554979</v>
       </c>
     </row>
   </sheetData>
@@ -4236,32 +4900,32 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="168" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="168" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="168" t="inlineStr">
         <is>
           <t>Déficit cuantitativo de vivienda</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="168" t="inlineStr">
         <is>
           <t>Déficit cualitativo de vivienda</t>
         </is>
@@ -4377,6 +5041,22 @@
       </c>
       <c r="D8">
         <v>0.218322123375406</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.154393190208715</v>
+      </c>
+      <c r="D9">
+        <v>0.269225033859051</v>
       </c>
     </row>
   </sheetData>
@@ -4388,50 +5068,50 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="79.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="80.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>Km de vía primaria por km² del municipio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>Km de vía secundaria por km² del municipio</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>Km de vía terciaria por km² del municipio</t>
         </is>
@@ -4456,13 +5136,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="38">
         <v>0.0007168839960829</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="40">
         <v>0.0187946087620119</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="42">
         <v>0.304287966951957</v>
       </c>
     </row>
@@ -4485,13 +5165,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="38">
         <v>0</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="40">
         <v>0.159422521991818</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="42">
         <v>0.462739600954249</v>
       </c>
     </row>
@@ -4514,13 +5194,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="38">
         <v>0.529915488973597</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="40">
         <v>0.0386012507935566</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="42">
         <v>0.463856080277718</v>
       </c>
     </row>
@@ -4543,13 +5223,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="38">
         <v>0</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="40">
         <v>0.366844188144731</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="42">
         <v>0.343234054239572</v>
       </c>
     </row>
@@ -4572,13 +5252,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="38">
         <v>0</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="40">
         <v>0.229657082986331</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="42">
         <v>0.623257718966958</v>
       </c>
     </row>
@@ -4601,13 +5281,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="38">
         <v>0</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="40">
         <v>0.0459687419596133</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="42">
         <v>0.340703183283503</v>
       </c>
     </row>
@@ -4630,45 +5310,74 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="38">
         <v>0.456887205473553</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="40">
         <v>0.180649866301896</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="42">
         <v>0.300497069185951</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="38">
+        <v>0.197305225545038</v>
+      </c>
+      <c r="F9" s="40">
+        <v>0.0582634956810358</v>
+      </c>
+      <c r="G9" s="42">
+        <v>0.217249847422121</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por área del municipio)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="33">
-        <v>0.0938754803900583</v>
-      </c>
-      <c r="F9" s="35">
-        <v>0.115292981862803</v>
-      </c>
-      <c r="G9" s="37">
-        <v>0.375661153447804</v>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="39">
+        <v>0.123405233214913</v>
+      </c>
+      <c r="F10" s="41">
+        <v>0.099010754461463</v>
+      </c>
+      <c r="G10" s="43">
+        <v>0.330433866997552</v>
       </c>
     </row>
   </sheetData>
@@ -4680,50 +5389,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="71.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Km de vía primaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Km de vía secundaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Km de vía terciaria por cada 1.000 hab.</t>
         </is>
@@ -4748,13 +5457,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="47">
         <v>0.0256632093782915</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="49">
         <v>0.672814545279404</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="51">
         <v>10.8929838716611</v>
       </c>
     </row>
@@ -4777,13 +5486,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="47">
         <v>0</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="49">
         <v>2.98133097019221</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="51">
         <v>8.6536073211167</v>
       </c>
     </row>
@@ -4806,13 +5515,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="47">
         <v>8.3925110236849</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="49">
         <v>0.611345449517688</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="51">
         <v>7.34629832140645</v>
       </c>
     </row>
@@ -4835,13 +5544,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="47">
         <v>0</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="49">
         <v>7.41724830014554</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="51">
         <v>6.93987335123355</v>
       </c>
     </row>
@@ -4864,13 +5573,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="47">
         <v>0</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="49">
         <v>6.06834601407636</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="51">
         <v>16.468655986807</v>
       </c>
     </row>
@@ -4893,13 +5602,13 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="47">
         <v>0</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="49">
         <v>1.27365052805511</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="51">
         <v>9.43982303627831</v>
       </c>
     </row>
@@ -4922,45 +5631,74 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="47">
         <v>4.50148119296098</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="49">
         <v>1.77985280814779</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="51">
         <v>2.96064737483386</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="47">
+        <v>3.72607120920584</v>
+      </c>
+      <c r="F9" s="49">
+        <v>1.10029490199813</v>
+      </c>
+      <c r="G9" s="51">
+        <v>4.10272155462578</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="39">
-        <v>1.94378339939616</v>
-      </c>
-      <c r="F9" s="41">
-        <v>2.38822842354729</v>
-      </c>
-      <c r="G9" s="43">
-        <v>7.7880911134049</v>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="48">
+        <v>2.48687003085008</v>
+      </c>
+      <c r="F10" s="50">
+        <v>1.99577807186733</v>
+      </c>
+      <c r="G10" s="52">
+        <v>6.66511034210405</v>
       </c>
     </row>
   </sheetData>
@@ -4972,74 +5710,74 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral total ($)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral urbano ($)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral rural ($)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral urbano sobre el total</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral rural sobre el total</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro urbano</t>
         </is>
@@ -5064,19 +5802,19 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="56">
         <v>118798373000</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="58">
         <v>75154951000</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="60">
         <v>43643422000</v>
       </c>
-      <c r="H2" s="50">
+      <c r="H2" s="62">
         <v>0.632626096655381</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="64">
         <v>0.367373903344619</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -5109,19 +5847,19 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="56">
         <v>321681771000</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="58">
         <v>100729369000</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="60">
         <v>220952402000</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="62">
         <v>0.313133593759032</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="64">
         <v>0.686866406240968</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -5154,19 +5892,19 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="56">
         <v>76671937000</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="58">
         <v>43049771000</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="60">
         <v>33622166000</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="62">
         <v>0.561480154075148</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="64">
         <v>0.438519845924853</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -5199,19 +5937,19 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="56">
         <v>158567398000</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="58">
         <v>45101557000</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="60">
         <v>113465841000</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="62">
         <v>0.284431463017385</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="64">
         <v>0.715568536982615</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -5244,19 +5982,19 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <v>255620707523</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="58">
         <v>75510483000</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="60">
         <v>180110224523</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="62">
         <v>0.295400492908838</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="64">
         <v>0.704599507091162</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -5289,19 +6027,19 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="56">
         <v>204890178000</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="58">
         <v>135811600000</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="60">
         <v>69078578000</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="62">
         <v>0.662850710198514</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="64">
         <v>0.337149289801486</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -5334,19 +6072,19 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="56">
         <v>1904004748000</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="58">
         <v>1108211071000</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="60">
         <v>795793677000</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="62">
         <v>0.582042178289778</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="64">
         <v>0.417957821710222</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -5361,47 +6099,92 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="56">
+        <v>3276017752492</v>
+      </c>
+      <c r="F9" s="58">
+        <v>1528687230009</v>
+      </c>
+      <c r="G9" s="60">
+        <v>1747330522483</v>
+      </c>
+      <c r="H9" s="62">
+        <v>0.466629714947716</v>
+      </c>
+      <c r="I9" s="64">
+        <v>0.533370285052284</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ajuste pendiente</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ajuste pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="45">
-        <v>3040235112523</v>
-      </c>
-      <c r="F9" s="47">
-        <v>1583568802000</v>
-      </c>
-      <c r="G9" s="49">
-        <v>1456666310523</v>
-      </c>
-      <c r="H9" s="51">
-        <v>0.520870506191162</v>
-      </c>
-      <c r="I9" s="53">
-        <v>0.479129493808838</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="57">
+        <v>6316252865015</v>
+      </c>
+      <c r="F10" s="59">
+        <v>3112256032009</v>
+      </c>
+      <c r="G10" s="61">
+        <v>3203996833006</v>
+      </c>
+      <c r="H10" s="63">
+        <v>0.492737719423399</v>
+      </c>
+      <c r="I10" s="65">
+        <v>0.507262280576601</v>
+      </c>
+      <c r="J10" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5416,103 +6199,103 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="75.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="76.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="67" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="67" t="inlineStr">
         <is>
           <t>IMCA total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="67" t="inlineStr">
         <is>
           <t>IMCA adopción TIC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="67" t="inlineStr">
         <is>
           <t>IMCA capacidades</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="67" t="inlineStr">
         <is>
           <t>IMCA dinamismo de los negocios</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="67" t="inlineStr">
         <is>
           <t>IMCA infraestructura</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="67" t="inlineStr">
         <is>
           <t>IMCA innovación</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="67" t="inlineStr">
         <is>
           <t>IMCA instituciones</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado de bienes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado laboral</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="67" t="inlineStr">
         <is>
           <t>IMCA salud</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="67" t="inlineStr">
         <is>
           <t>IMCA sistema financiero</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="67" t="inlineStr">
         <is>
           <t>IMCA tamaño del mercado</t>
         </is>
@@ -5537,40 +6320,40 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="69">
         <v>29.6182126982757</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="71">
         <v>5.16472276562765</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="73">
         <v>27.8530931948171</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="75">
         <v>58.6098219745333</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="77">
         <v>44.2377208438223</v>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="79">
         <v>0</v>
       </c>
-      <c r="K2" s="66">
+      <c r="K2" s="81">
         <v>50.4835898393931</v>
       </c>
-      <c r="L2" s="68">
+      <c r="L2" s="83">
         <v>7.22951858359784</v>
       </c>
-      <c r="M2" s="70">
+      <c r="M2" s="85">
         <v>58.2128607806214</v>
       </c>
-      <c r="N2" s="72">
+      <c r="N2" s="87">
         <v>43.6948382608985</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="89">
         <v>7.52653265205133</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="91">
         <v>22.7876407856698</v>
       </c>
     </row>
@@ -5593,40 +6376,40 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="69">
         <v>29.9068801817519</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="71">
         <v>12.4549182460586</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="73">
         <v>36.0512603955891</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="75">
         <v>65.1251583825062</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I3" s="77">
         <v>45.4735124211813</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="79">
         <v>0</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="81">
         <v>55.4769526360818</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="83">
         <v>5.41254806000367</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="85">
         <v>28.080024676547</v>
       </c>
-      <c r="N3" s="72">
+      <c r="N3" s="87">
         <v>42.5838646698037</v>
       </c>
-      <c r="O3" s="74">
+      <c r="O3" s="89">
         <v>17.4827981932103</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="91">
         <v>20.8346443182895</v>
       </c>
     </row>
@@ -5649,40 +6432,40 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="69">
         <v>32.9996465485612</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="71">
         <v>2.30860655192213</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="73">
         <v>52.1865800116513</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="75">
         <v>67.4250766784178</v>
       </c>
-      <c r="I4" s="62">
+      <c r="I4" s="77">
         <v>42.2877771283633</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="79">
         <v>0</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="81">
         <v>54.7797760721437</v>
       </c>
-      <c r="L4" s="68">
+      <c r="L4" s="83">
         <v>18.9199722255257</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="85">
         <v>46.4756875510381</v>
       </c>
-      <c r="N4" s="72">
+      <c r="N4" s="87">
         <v>48.7198411654256</v>
       </c>
-      <c r="O4" s="74">
+      <c r="O4" s="89">
         <v>15.7622351078213</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="91">
         <v>14.1305595418645</v>
       </c>
     </row>
@@ -5705,40 +6488,40 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="69">
         <v>31.2762099450875</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="71">
         <v>14.9478905090642</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="73">
         <v>47.3242706817593</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="75">
         <v>64.3661869361983</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="77">
         <v>47.8891636665712</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="79">
         <v>0</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="81">
         <v>49.662940455015</v>
       </c>
-      <c r="L5" s="68">
+      <c r="L5" s="83">
         <v>6.545705464163</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="85">
         <v>32.2187877976652</v>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="87">
         <v>36.3666519956173</v>
       </c>
-      <c r="O5" s="74">
+      <c r="O5" s="89">
         <v>23.6938871351707</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="91">
         <v>21.0228247547386</v>
       </c>
     </row>
@@ -5761,40 +6544,40 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="69">
         <v>29.7817367328996</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="71">
         <v>10.5150194160258</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="73">
         <v>38.5737120732943</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="75">
         <v>62.6942250844414</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="77">
         <v>43.0383077489036</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="79">
         <v>0</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="81">
         <v>60.3658076288784</v>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="83">
         <v>4.45576423148076</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="85">
         <v>35.2700836833198</v>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="87">
         <v>47.0783446140918</v>
       </c>
-      <c r="O6" s="74">
+      <c r="O6" s="89">
         <v>5.70830379298121</v>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="91">
         <v>19.8995357884783</v>
       </c>
     </row>
@@ -5817,40 +6600,40 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="69">
         <v>28.3680895313091</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="71">
         <v>6.16743759621286</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="73">
         <v>34.2317830707463</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="75">
         <v>57.5335133734781</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="77">
         <v>40.943744232424</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="79">
         <v>0</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="81">
         <v>50.2049204470031</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="83">
         <v>4.59808268498587</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="85">
         <v>40.6401057388193</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="87">
         <v>39.7543261454828</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="89">
         <v>22.0988633833755</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="91">
         <v>15.876208171872</v>
       </c>
     </row>
@@ -5873,156 +6656,212 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="69">
         <v>33.9213813312533</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="71">
         <v>25.9343611549181</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="73">
         <v>41.9398943865524</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="75">
         <v>64.973107668511</v>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="77">
         <v>53.9783938850318</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="79">
         <v>0</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="81">
         <v>55.5148242396596</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="83">
         <v>11.0235260796342</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="85">
         <v>36.608792323912</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="87">
         <v>39.049777829756</v>
       </c>
-      <c r="O8" s="74">
+      <c r="O8" s="89">
         <v>19.129382212348</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="91">
         <v>24.9831348634628</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="69">
+        <v>41.6425114913387</v>
+      </c>
+      <c r="F9" s="71">
+        <v>41.4637249436746</v>
+      </c>
+      <c r="G9" s="73">
+        <v>46.2292787722391</v>
+      </c>
+      <c r="H9" s="75">
+        <v>65.5394429129094</v>
+      </c>
+      <c r="I9" s="77">
+        <v>56.6266795970908</v>
+      </c>
+      <c r="J9" s="79">
+        <v>0</v>
+      </c>
+      <c r="K9" s="81">
+        <v>58.0739469751954</v>
+      </c>
+      <c r="L9" s="83">
+        <v>22.0129744397473</v>
+      </c>
+      <c r="M9" s="85">
+        <v>47.5274689852476</v>
+      </c>
+      <c r="N9" s="87">
+        <v>46.0335579187043</v>
+      </c>
+      <c r="O9" s="89">
+        <v>54.8743863952761</v>
+      </c>
+      <c r="P9" s="91">
+        <v>19.686165464641</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población 2022)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="55">
-        <v>31.068388624218</v>
-      </c>
-      <c r="F9" s="57">
-        <v>13.0181560399089</v>
-      </c>
-      <c r="G9" s="59">
-        <v>38.6540601918846</v>
-      </c>
-      <c r="H9" s="61">
-        <v>62.9410120509248</v>
-      </c>
-      <c r="I9" s="63">
-        <v>46.5824308656337</v>
-      </c>
-      <c r="J9" s="65">
+      <c r="C10" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="70">
+        <v>34.2919173919462</v>
+      </c>
+      <c r="F10" s="72">
+        <v>21.6898076584845</v>
+      </c>
+      <c r="G10" s="74">
+        <v>40.9633708857797</v>
+      </c>
+      <c r="H10" s="76">
+        <v>63.7331455205107</v>
+      </c>
+      <c r="I10" s="78">
+        <v>49.6444271317019</v>
+      </c>
+      <c r="J10" s="80">
         <v>0</v>
       </c>
-      <c r="K9" s="67">
-        <v>53.5783768403641</v>
-      </c>
-      <c r="L9" s="69">
-        <v>8.32937307029902</v>
-      </c>
-      <c r="M9" s="71">
-        <v>39.3454022202241</v>
-      </c>
-      <c r="N9" s="73">
-        <v>41.6677968270623</v>
-      </c>
-      <c r="O9" s="75">
-        <v>16.8296118866458</v>
-      </c>
-      <c r="P9" s="77">
-        <v>20.806054873451</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="K10" s="82">
+        <v>54.9488545470332</v>
+      </c>
+      <c r="L10" s="84">
+        <v>12.5008285389787</v>
+      </c>
+      <c r="M10" s="86">
+        <v>41.8397110085717</v>
+      </c>
+      <c r="N10" s="88">
+        <v>42.9987021559284</v>
+      </c>
+      <c r="O10" s="90">
+        <v>28.4275880622052</v>
+      </c>
+      <c r="P10" s="92">
+        <v>20.4646558022147</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11" s="68" t="inlineStr">
         <is>
           <t>SUBREGIÓN OCCIDENTE (IMCA oficial de subregión)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="68" t="inlineStr">
         <is>
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" s="55">
+      <c r="D11" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" s="70">
         <v>31.7778750125919</v>
       </c>
-      <c r="F10" s="57">
+      <c r="F11" s="72">
         <v>11.1355997417811</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G11" s="74">
         <v>39.8497905507535</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H11" s="76">
         <v>61.508126443671</v>
       </c>
-      <c r="I10" s="63">
+      <c r="I11" s="78">
         <v>44.8418590365667</v>
       </c>
-      <c r="J10" s="65">
+      <c r="J11" s="80">
         <v>0</v>
       </c>
-      <c r="K10" s="67">
+      <c r="K11" s="82">
         <v>49.9944215409497</v>
       </c>
-      <c r="L10" s="69">
+      <c r="L11" s="84">
         <v>6.97918002835241</v>
       </c>
-      <c r="M10" s="71">
+      <c r="M11" s="86">
         <v>46.8257087011245</v>
       </c>
-      <c r="N10" s="73">
+      <c r="N11" s="88">
         <v>45.1217806507044</v>
       </c>
-      <c r="O10" s="75">
+      <c r="O11" s="90">
         <v>25.2427616863391</v>
       </c>
-      <c r="P10" s="77">
+      <c r="P11" s="92">
         <v>18.0573967582682</v>
       </c>
     </row>
@@ -6035,104 +6874,104 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="75.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="76.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="94" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="94" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="94" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="94" t="inlineStr">
         <is>
           <t>Índice de Gobierno Digital</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="94" t="inlineStr">
         <is>
           <t>Gobernanza</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="94" t="inlineStr">
         <is>
           <t>Innovación Pública Digital</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="94" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="94" t="inlineStr">
         <is>
           <t>Seguridad y Privacidad de la Información</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="94" t="inlineStr">
         <is>
           <t>Servicios Ciudadanos Digitales</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="94" t="inlineStr">
         <is>
           <t>Cultura y Apropiación</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="94" t="inlineStr">
         <is>
           <t>Servicios y Procesos Inteligentes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="94" t="inlineStr">
         <is>
           <t>Estado Abierto</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="94" t="inlineStr">
         <is>
           <t>Decisiones basadas en datos</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="94" t="inlineStr">
         <is>
           <t>Proyectos de Transformación Digital</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="94" t="inlineStr">
         <is>
           <t>Estrategias de Ciudades y Territorios Inteligentes</t>
         </is>
@@ -6157,42 +6996,42 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="78">
+      <c r="E2" s="96">
         <v>50.41</v>
       </c>
-      <c r="F2" s="80">
+      <c r="F2" s="98">
         <v>88.89</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="100">
         <v>0</v>
       </c>
-      <c r="H2" s="84">
+      <c r="H2" s="102">
         <v>43.06</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="104">
         <v>50</v>
       </c>
-      <c r="J2" s="88">
+      <c r="J2" s="106">
         <v>75</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="108">
         <v>80</v>
       </c>
-      <c r="L2" s="92">
+      <c r="L2" s="110">
         <v>0</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="112">
         <v>65</v>
       </c>
-      <c r="N2" s="96">
+      <c r="N2" s="114">
         <v>27.59</v>
       </c>
-      <c r="O2" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" s="100">
+      <c r="O2" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" s="118">
         <v>61</v>
       </c>
     </row>
@@ -6215,42 +7054,42 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="96">
         <v>23.93</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="98">
         <v>58.33</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="100">
         <v>0</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="102">
         <v>16.67</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="104">
         <v>37.5</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="106">
         <v>0</v>
       </c>
-      <c r="K3" s="90">
+      <c r="K3" s="108">
         <v>0</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="110">
         <v>0</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="112">
         <v>25.33</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="114">
         <v>20</v>
       </c>
-      <c r="O3" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" s="100" t="inlineStr">
+      <c r="O3" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6275,40 +7114,40 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="96">
         <v>35.37</v>
       </c>
-      <c r="F4" s="80">
+      <c r="F4" s="98">
         <v>69.56</v>
       </c>
-      <c r="G4" s="82">
+      <c r="G4" s="100">
         <v>89</v>
       </c>
-      <c r="H4" s="84">
+      <c r="H4" s="102">
         <v>34.72</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="104">
         <v>75</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="106">
         <v>93.4</v>
       </c>
-      <c r="K4" s="90">
+      <c r="K4" s="108">
         <v>60</v>
       </c>
-      <c r="L4" s="92">
+      <c r="L4" s="110">
         <v>22.22</v>
       </c>
-      <c r="M4" s="94">
+      <c r="M4" s="112">
         <v>23.78</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="114">
         <v>20.69</v>
       </c>
-      <c r="O4" s="98">
+      <c r="O4" s="116">
         <v>66.67</v>
       </c>
-      <c r="P4" s="100" t="inlineStr">
+      <c r="P4" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6333,42 +7172,42 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="96">
         <v>51.7</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="98">
         <v>58.33</v>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="100">
         <v>0</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="102">
         <v>0</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="104">
         <v>25</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="106">
         <v>66.67</v>
       </c>
-      <c r="K5" s="90">
+      <c r="K5" s="108">
         <v>68</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="110">
         <v>0</v>
       </c>
-      <c r="M5" s="94">
+      <c r="M5" s="112">
         <v>74.67</v>
       </c>
-      <c r="N5" s="96">
+      <c r="N5" s="114">
         <v>10.34</v>
       </c>
-      <c r="O5" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" s="100" t="inlineStr">
+      <c r="O5" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6393,42 +7232,42 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="96">
         <v>54.76</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="98">
         <v>25.08</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="100">
         <v>0</v>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="102">
         <v>0</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="104">
         <v>33.25</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="106">
         <v>0</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="108">
         <v>0</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="110">
         <v>16.67</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="112">
         <v>74.67</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="114">
         <v>44.83</v>
       </c>
-      <c r="O6" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" s="100" t="inlineStr">
+      <c r="O6" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6453,42 +7292,42 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="96">
         <v>50.7</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="98">
         <v>69.39</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="100">
         <v>0</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="102">
         <v>15.56</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="104">
         <v>0</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="106">
         <v>33.33</v>
       </c>
-      <c r="K7" s="90">
+      <c r="K7" s="108">
         <v>0</v>
       </c>
-      <c r="L7" s="92">
+      <c r="L7" s="110">
         <v>0</v>
       </c>
-      <c r="M7" s="94">
+      <c r="M7" s="112">
         <v>58.67</v>
       </c>
-      <c r="N7" s="96">
+      <c r="N7" s="114">
         <v>62.07</v>
       </c>
-      <c r="O7" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" s="100">
+      <c r="O7" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" s="118">
         <v>100</v>
       </c>
     </row>
@@ -6511,158 +7350,214 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="96">
         <v>77.79</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="98">
         <v>88.83</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="100">
         <v>45.75</v>
       </c>
-      <c r="H8" s="84">
+      <c r="H8" s="102">
         <v>22.22</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="104">
         <v>80.58</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="106">
         <v>33.33</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="108">
         <v>100</v>
       </c>
-      <c r="L8" s="92">
+      <c r="L8" s="110">
         <v>41.07</v>
       </c>
-      <c r="M8" s="94">
+      <c r="M8" s="112">
         <v>98.67</v>
       </c>
-      <c r="N8" s="96">
+      <c r="N8" s="114">
         <v>72.41</v>
       </c>
-      <c r="O8" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P8" s="100">
+      <c r="O8" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" s="118">
         <v>50</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="96">
+        <v>87.64</v>
+      </c>
+      <c r="F9" s="98">
+        <v>100</v>
+      </c>
+      <c r="G9" s="100">
+        <v>94.5</v>
+      </c>
+      <c r="H9" s="102">
+        <v>75</v>
+      </c>
+      <c r="I9" s="104">
+        <v>70.86</v>
+      </c>
+      <c r="J9" s="106">
+        <v>93.4</v>
+      </c>
+      <c r="K9" s="108">
+        <v>100</v>
+      </c>
+      <c r="L9" s="110">
+        <v>33.33</v>
+      </c>
+      <c r="M9" s="112">
+        <v>93.9</v>
+      </c>
+      <c r="N9" s="114">
+        <v>96.55</v>
+      </c>
+      <c r="O9" s="116">
+        <v>100</v>
+      </c>
+      <c r="P9" s="118">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población 2024)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="79">
-        <v>51.147936416185</v>
-      </c>
-      <c r="F9" s="81">
-        <v>71.9623830651461</v>
-      </c>
-      <c r="G9" s="83">
-        <v>20.0833658803312</v>
-      </c>
-      <c r="H9" s="85">
-        <v>21.389136697391</v>
-      </c>
-      <c r="I9" s="87">
-        <v>47.0526038119044</v>
-      </c>
-      <c r="J9" s="89">
-        <v>40.0164197781597</v>
-      </c>
-      <c r="K9" s="91">
-        <v>49.9566942665209</v>
-      </c>
-      <c r="L9" s="93">
-        <v>13.5224633650992</v>
-      </c>
-      <c r="M9" s="95">
-        <v>62.3036156850492</v>
-      </c>
-      <c r="N9" s="97">
-        <v>41.5432229339166</v>
-      </c>
-      <c r="O9" s="99">
-        <v>66.67</v>
-      </c>
-      <c r="P9" s="101">
-        <v>66.4046816272386</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C10" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="97">
+        <v>62.2665222303088</v>
+      </c>
+      <c r="F10" s="99">
+        <v>80.5050254727946</v>
+      </c>
+      <c r="G10" s="101">
+        <v>42.7570009450461</v>
+      </c>
+      <c r="H10" s="103">
+        <v>37.7235646704831</v>
+      </c>
+      <c r="I10" s="105">
+        <v>54.3063612465919</v>
+      </c>
+      <c r="J10" s="107">
+        <v>56.2815979969367</v>
+      </c>
+      <c r="K10" s="109">
+        <v>65.2041408227333</v>
+      </c>
+      <c r="L10" s="111">
+        <v>19.5575234360573</v>
+      </c>
+      <c r="M10" s="113">
+        <v>71.9305612704896</v>
+      </c>
+      <c r="N10" s="115">
+        <v>58.3029649463931</v>
+      </c>
+      <c r="O10" s="117">
+        <v>94.1565685640362</v>
+      </c>
+      <c r="P10" s="119">
+        <v>81.0749459000825</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="95" t="inlineStr">
         <is>
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" s="79">
+      <c r="D11" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" s="97">
         <v>56.2273877097285</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F11" s="99">
         <v>68.8539535176784</v>
       </c>
-      <c r="G10" s="83">
+      <c r="G11" s="101">
         <v>26.9006294105998</v>
       </c>
-      <c r="H10" s="85">
+      <c r="H11" s="103">
         <v>26.4851025239433</v>
       </c>
-      <c r="I10" s="87">
+      <c r="I11" s="105">
         <v>50.4553803467272</v>
       </c>
-      <c r="J10" s="89">
+      <c r="J11" s="107">
         <v>36.7239335349608</v>
       </c>
-      <c r="K10" s="91">
+      <c r="K11" s="109">
         <v>58.8624628249442</v>
       </c>
-      <c r="L10" s="93">
+      <c r="L11" s="111">
         <v>10.1003311550371</v>
       </c>
-      <c r="M10" s="95">
+      <c r="M11" s="113">
         <v>69.1296690249874</v>
       </c>
-      <c r="N10" s="97">
+      <c r="N11" s="115">
         <v>42.6351604918269</v>
       </c>
-      <c r="O10" s="99">
+      <c r="O11" s="117">
         <v>81.6760874554875</v>
       </c>
-      <c r="P10" s="101">
+      <c r="P11" s="119">
         <v>81.0749459000825</v>
       </c>
     </row>
@@ -6675,38 +7570,38 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="121" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="121" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="121" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="121" t="inlineStr">
         <is>
           <t>Tasa de tránsito inmediato a la educación superior</t>
         </is>
@@ -6731,7 +7626,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="102">
+      <c r="E2" s="123">
         <v>0.3</v>
       </c>
     </row>
@@ -6754,7 +7649,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="123">
         <v>0.285714285714286</v>
       </c>
     </row>
@@ -6777,7 +7672,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="123">
         <v>0.411764705882353</v>
       </c>
     </row>
@@ -6800,7 +7695,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="123">
         <v>0.294117647058824</v>
       </c>
     </row>
@@ -6823,7 +7718,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="102">
+      <c r="E6" s="123">
         <v>0.290322580645161</v>
       </c>
     </row>
@@ -6846,7 +7741,7 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="102">
+      <c r="E7" s="123">
         <v>0.36986301369863</v>
       </c>
     </row>
@@ -6869,33 +7764,56 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="102">
+      <c r="E8" s="123">
         <v>0.299270072992701</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="123">
+        <v>0.380782918149466</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="122" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="103">
-        <v>0.321578900855993</v>
+      <c r="C10" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="124">
+        <v>0.328979403017678</v>
       </c>
     </row>
   </sheetData>
@@ -6907,56 +7825,56 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="91.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="126" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="126" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="126" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="126" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por fibra óptica</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="126" t="inlineStr">
         <is>
           <t>Proporción de líneas sobre fibra óptica</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por cada 1.000 habitantes</t>
         </is>
@@ -6981,17 +7899,17 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E2" s="104">
-        <v>4001</v>
-      </c>
-      <c r="F2" s="106">
-        <v>859</v>
-      </c>
-      <c r="G2" s="108">
-        <v>0.21469632591852</v>
-      </c>
-      <c r="H2" s="110">
-        <v>363.231956423059</v>
+      <c r="E2" s="128">
+        <v>1167</v>
+      </c>
+      <c r="F2" s="130">
+        <v>453</v>
+      </c>
+      <c r="G2" s="132">
+        <v>0.388174807197943</v>
+      </c>
+      <c r="H2" s="134">
+        <v>105.946436677258</v>
       </c>
     </row>
     <row r="3">
@@ -7013,17 +7931,17 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E3" s="104">
-        <v>7429</v>
-      </c>
-      <c r="F3" s="106">
-        <v>118</v>
-      </c>
-      <c r="G3" s="108">
-        <v>0.0158836990173644</v>
-      </c>
-      <c r="H3" s="110">
-        <v>589.042182048842</v>
+      <c r="E3" s="128">
+        <v>2527</v>
+      </c>
+      <c r="F3" s="130">
+        <v>4</v>
+      </c>
+      <c r="G3" s="132">
+        <v>0.00158290462999604</v>
+      </c>
+      <c r="H3" s="134">
+        <v>200.364732001269</v>
       </c>
     </row>
     <row r="4">
@@ -7045,17 +7963,17 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E4" s="104">
-        <v>1475</v>
-      </c>
-      <c r="F4" s="106">
-        <v>137</v>
-      </c>
-      <c r="G4" s="108">
-        <v>0.0928813559322034</v>
-      </c>
-      <c r="H4" s="110">
-        <v>230.324797001874</v>
+      <c r="E4" s="128">
+        <v>400</v>
+      </c>
+      <c r="F4" s="130">
+        <v>46</v>
+      </c>
+      <c r="G4" s="132">
+        <v>0.115</v>
+      </c>
+      <c r="H4" s="134">
+        <v>62.4609618988132</v>
       </c>
     </row>
     <row r="5">
@@ -7077,17 +7995,17 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E5" s="104">
-        <v>3047</v>
-      </c>
-      <c r="F5" s="106">
-        <v>39</v>
-      </c>
-      <c r="G5" s="108">
-        <v>0.0127994748933377</v>
-      </c>
-      <c r="H5" s="110">
-        <v>604.803493449782</v>
+      <c r="E5" s="128">
+        <v>986</v>
+      </c>
+      <c r="F5" s="130">
+        <v>0</v>
+      </c>
+      <c r="G5" s="132">
+        <v>0</v>
+      </c>
+      <c r="H5" s="134">
+        <v>195.712584358873</v>
       </c>
     </row>
     <row r="6">
@@ -7109,17 +8027,17 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E6" s="104">
-        <v>468</v>
-      </c>
-      <c r="F6" s="106">
-        <v>18</v>
-      </c>
-      <c r="G6" s="108">
-        <v>0.0384615384615385</v>
-      </c>
-      <c r="H6" s="110">
-        <v>134.909195733641</v>
+      <c r="E6" s="128">
+        <v>175</v>
+      </c>
+      <c r="F6" s="130">
+        <v>2</v>
+      </c>
+      <c r="G6" s="132">
+        <v>0.0114285714285714</v>
+      </c>
+      <c r="H6" s="134">
+        <v>50.4468146439896</v>
       </c>
     </row>
     <row r="7">
@@ -7141,17 +8059,17 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E7" s="104">
-        <v>1730</v>
-      </c>
-      <c r="F7" s="106">
-        <v>795</v>
-      </c>
-      <c r="G7" s="108">
-        <v>0.459537572254335</v>
-      </c>
-      <c r="H7" s="110">
-        <v>174.588757695025</v>
+      <c r="E7" s="128">
+        <v>517</v>
+      </c>
+      <c r="F7" s="130">
+        <v>379</v>
+      </c>
+      <c r="G7" s="132">
+        <v>0.733075435203095</v>
+      </c>
+      <c r="H7" s="134">
+        <v>52.1747905944091</v>
       </c>
     </row>
     <row r="8">
@@ -7173,51 +8091,83 @@
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
-      <c r="E8" s="104">
-        <v>7372</v>
-      </c>
-      <c r="F8" s="106">
-        <v>1548</v>
-      </c>
-      <c r="G8" s="108">
-        <v>0.209983722192078</v>
-      </c>
-      <c r="H8" s="110">
-        <v>401.853366039793</v>
+      <c r="E8" s="128">
+        <v>2155</v>
+      </c>
+      <c r="F8" s="130">
+        <v>212</v>
+      </c>
+      <c r="G8" s="132">
+        <v>0.0983758700696056</v>
+      </c>
+      <c r="H8" s="134">
+        <v>117.470700463342</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO SIMPLE PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="105">
-        <v>3646</v>
-      </c>
-      <c r="F9" s="107">
-        <v>502</v>
-      </c>
-      <c r="G9" s="109">
-        <v>0.149177669809911</v>
-      </c>
-      <c r="H9" s="111">
-        <v>356.964821198859</v>
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="128">
+        <v>4238</v>
+      </c>
+      <c r="F9" s="130">
+        <v>3615</v>
+      </c>
+      <c r="G9" s="132">
+        <v>0.852996696554979</v>
+      </c>
+      <c r="H9" s="134">
+        <v>149.115090953872</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="127" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURÍSTICA Y AGROECOLÓGICA (suma de líneas; razones recalculadas sobre las sumas)</t>
+        </is>
+      </c>
+      <c r="C10" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="129">
+        <v>12165</v>
+      </c>
+      <c r="F10" s="131">
+        <v>4711</v>
+      </c>
+      <c r="G10" s="133">
+        <v>0.387258528565557</v>
+      </c>
+      <c r="H10" s="135">
+        <v>127.766166384842</v>
       </c>
     </row>
   </sheetData>
